--- a/ショートカットキー一覧.xlsx
+++ b/ショートカットキー一覧.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FA6499-9276-4533-B278-DC0F38B6CAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3574FCA2-CC40-4780-A3AF-6E3B872CDA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32385" yWindow="630" windowWidth="32385" windowHeight="40695" firstSheet="11" activeTab="20" xr2:uid="{43490DDC-BDDE-46A2-A177-1DE0A5EB93B9}"/>
+    <workbookView xWindow="-32385" yWindow="1230" windowWidth="32385" windowHeight="40695" firstSheet="21" activeTab="31" xr2:uid="{43490DDC-BDDE-46A2-A177-1DE0A5EB93B9}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="46" r:id="rId1"/>
@@ -39,6 +39,7 @@
     <sheet name="▼VSCode" sheetId="43" r:id="rId29"/>
     <sheet name="▼VSCode(Ctrl+K)" sheetId="44" r:id="rId30"/>
     <sheet name="▽WinMerge" sheetId="47" r:id="rId31"/>
+    <sheet name="▽Blender" sheetId="49" r:id="rId32"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">▼Excel!$A$68:$K$68</definedName>
@@ -54,6 +55,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'▼X-Finder'!$A$1:$I$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">▼秀丸!$A$1:$I$87</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">テーブル1713[[#All],[Ctrl]:[機能]]</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="31">テーブル178101120[[#All],[Ctrl]:[機能]]</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">▼Excel!$A$1:$I$92</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">テーブル178[[#All],[Ctrl]:[機能]]</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'▽Excel(alt)'!$A$1:$B$57</definedName>
@@ -184,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11346" uniqueCount="1816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11362" uniqueCount="1818">
   <si>
     <t>Ctrl</t>
   </si>
@@ -8971,6 +8973,35 @@
   </si>
   <si>
     <t>WSL2ファイルパスコピー</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>オブジェクトモード/編集モード切替</t>
+    <rPh sb="10" eb="12">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キリカエ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>オブジェクトのモード(例: 移動/回転)切替え</t>
+    <rPh sb="11" eb="12">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カイテン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カ</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -9313,7 +9344,7 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9495,12 +9526,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="ハイパーリンク" xfId="4" builtinId="8"/>
@@ -9509,7 +9534,242 @@
     <cellStyle name="標準 3" xfId="2" xr:uid="{6574F17E-666C-4C25-887B-BEC40B73B388}"/>
     <cellStyle name="標準 4" xfId="3" xr:uid="{6F24FA43-F5C8-47AC-8D09-3CBCB56FE905}"/>
   </cellStyles>
-  <dxfs count="253">
+  <dxfs count="266">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="ＭＳ ゴシック"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="ＭＳ ゴシック"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="ＭＳ ゴシック"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="ＭＳ ゴシック"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="ＭＳ ゴシック"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="ＭＳ ゴシック"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="ＭＳ ゴシック"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="ＭＳ ゴシック"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="ＭＳ ゴシック"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="ＭＳ ゴシック"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="ＭＳ ゴシック"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="ＭＳ ゴシック"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -14079,16 +14339,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="テーブル1345" displayName="テーブル1345" ref="A1:G87" headerRowDxfId="252" dataDxfId="251">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="テーブル1345" displayName="テーブル1345" ref="A1:G87" headerRowDxfId="265" dataDxfId="264">
   <autoFilter ref="A1:G87" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Ctrl" totalsRowLabel="集計" dataDxfId="250" totalsRowDxfId="249"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Shift" dataDxfId="248" totalsRowDxfId="247"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Alt" dataDxfId="246" totalsRowDxfId="245" dataCellStyle="標準 2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Win" dataDxfId="244" totalsRowDxfId="243"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Key" dataDxfId="242" totalsRowDxfId="241"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="機能" dataDxfId="240" totalsRowDxfId="239"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="|Ctrl|Shift|Alt|Win|Key|機能|" totalsRowFunction="count" dataDxfId="238" totalsRowDxfId="237" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Ctrl" totalsRowLabel="集計" dataDxfId="263" totalsRowDxfId="262"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Shift" dataDxfId="261" totalsRowDxfId="260"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Alt" dataDxfId="259" totalsRowDxfId="258" dataCellStyle="標準 2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Win" dataDxfId="257" totalsRowDxfId="256"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Key" dataDxfId="255" totalsRowDxfId="254"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="機能" dataDxfId="253" totalsRowDxfId="252"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="|Ctrl|Shift|Alt|Win|Key|機能|" totalsRowFunction="count" dataDxfId="251" totalsRowDxfId="250" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル1345[[#This Row],[機能]]),"","|"&amp;テーブル1345[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル1345[[#This Row],[Shift]]&amp;"|"&amp;テーブル1345[[#This Row],[Alt]]&amp;"|"&amp;テーブル1345[[#This Row],[Win]]&amp;"|"&amp;テーブル1345[[#This Row],[Key]]&amp;"|"&amp;テーブル1345[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14097,15 +14357,15 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="テーブル13" displayName="テーブル13" ref="A1:F90" headerRowDxfId="121" dataDxfId="120">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="テーブル13" displayName="テーブル13" ref="A1:F90" headerRowDxfId="134" dataDxfId="133">
   <autoFilter ref="A1:F90" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Ctrl" totalsRowLabel="集計" dataDxfId="119" totalsRowDxfId="118"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Shift" dataDxfId="117" totalsRowDxfId="116"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Alt" dataDxfId="115" totalsRowDxfId="114"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Key" dataDxfId="113" totalsRowDxfId="112"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="機能" dataDxfId="111" totalsRowDxfId="110"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="109" totalsRowDxfId="108" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Ctrl" totalsRowLabel="集計" dataDxfId="132" totalsRowDxfId="131"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Shift" dataDxfId="130" totalsRowDxfId="129"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Alt" dataDxfId="128" totalsRowDxfId="127"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Key" dataDxfId="126" totalsRowDxfId="125"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="機能" dataDxfId="124" totalsRowDxfId="123"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="122" totalsRowDxfId="121" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル13[[#This Row],[機能]]),"","|"&amp;テーブル13[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル13[[#This Row],[Shift]]&amp;"|"&amp;テーブル13[[#This Row],[Alt]]&amp;"|"&amp;テーブル13[[#This Row],[Key]]&amp;"|"&amp;テーブル13[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14114,15 +14374,15 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル1" displayName="テーブル1" ref="A1:F99" headerRowDxfId="107" dataDxfId="106">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル1" displayName="テーブル1" ref="A1:F99" headerRowDxfId="120" dataDxfId="119">
   <autoFilter ref="A1:F99" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Ctrl" totalsRowLabel="集計" dataDxfId="105" totalsRowDxfId="104"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Shift" dataDxfId="103" totalsRowDxfId="102"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Alt" dataDxfId="101" totalsRowDxfId="100"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Key" dataDxfId="99" totalsRowDxfId="98"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="機能" dataDxfId="97" totalsRowDxfId="96"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="95" totalsRowDxfId="94" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Ctrl" totalsRowLabel="集計" dataDxfId="118" totalsRowDxfId="117"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Shift" dataDxfId="116" totalsRowDxfId="115"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Alt" dataDxfId="114" totalsRowDxfId="113"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Key" dataDxfId="112" totalsRowDxfId="111"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="機能" dataDxfId="110" totalsRowDxfId="109"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="108" totalsRowDxfId="107" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル1[[#This Row],[機能]]),"","|"&amp;テーブル1[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル1[[#This Row],[Shift]]&amp;"|"&amp;テーブル1[[#This Row],[Alt]]&amp;"|"&amp;テーブル1[[#This Row],[Key]]&amp;"|"&amp;テーブル1[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14131,15 +14391,15 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="テーブル13456" displayName="テーブル13456" ref="A1:F78" headerRowDxfId="93" dataDxfId="92">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="テーブル13456" displayName="テーブル13456" ref="A1:F78" headerRowDxfId="106" dataDxfId="105">
   <autoFilter ref="A1:F78" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Ctrl" totalsRowLabel="集計" dataDxfId="91" totalsRowDxfId="90"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Shift" dataDxfId="89" totalsRowDxfId="88"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Alt" dataDxfId="87" totalsRowDxfId="86" dataCellStyle="標準 2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Key" dataDxfId="85" totalsRowDxfId="84"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="機能" dataDxfId="83" totalsRowDxfId="82"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="81" totalsRowDxfId="80" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Ctrl" totalsRowLabel="集計" dataDxfId="104" totalsRowDxfId="103"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Shift" dataDxfId="102" totalsRowDxfId="101"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Alt" dataDxfId="100" totalsRowDxfId="99" dataCellStyle="標準 2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Key" dataDxfId="98" totalsRowDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="機能" dataDxfId="96" totalsRowDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="94" totalsRowDxfId="93" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル13456[[#This Row],[機能]]),"","|"&amp;テーブル13456[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル13456[[#This Row],[Shift]]&amp;"|"&amp;テーブル13456[[#This Row],[Alt]]&amp;"|"&amp;テーブル13456[[#This Row],[Key]]&amp;"|"&amp;テーブル13456[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14148,15 +14408,15 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{54961AA9-FFDE-4BB4-AA20-F26900B51FF1}" name="テーブル1713" displayName="テーブル1713" ref="A1:F98" headerRowDxfId="79" dataDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{54961AA9-FFDE-4BB4-AA20-F26900B51FF1}" name="テーブル1713" displayName="テーブル1713" ref="A1:F98" headerRowDxfId="92" dataDxfId="91">
   <autoFilter ref="A1:F98" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{EBD26CAD-B172-41B3-A529-D3DA04293538}" name="Ctrl" totalsRowLabel="集計" dataDxfId="77" totalsRowDxfId="76"/>
-    <tableColumn id="2" xr3:uid="{2FD7451F-B63D-4E98-A795-D79A894B4E94}" name="Shift" dataDxfId="75" totalsRowDxfId="74"/>
-    <tableColumn id="3" xr3:uid="{A3D25D4C-366B-4D7B-84D3-B001BC845B0F}" name="Alt" dataDxfId="73" totalsRowDxfId="72"/>
-    <tableColumn id="4" xr3:uid="{71ED80D6-715B-4D58-BD43-ABA33B7EA76E}" name="Key" dataDxfId="71" totalsRowDxfId="70"/>
-    <tableColumn id="5" xr3:uid="{B8A9CB87-4538-4CB7-97B8-525338E383D6}" name="機能" dataDxfId="69" totalsRowDxfId="68"/>
-    <tableColumn id="7" xr3:uid="{06A85E02-878A-446D-B0C0-EDAC09D07E76}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="67" totalsRowDxfId="66" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{EBD26CAD-B172-41B3-A529-D3DA04293538}" name="Ctrl" totalsRowLabel="集計" dataDxfId="90" totalsRowDxfId="89"/>
+    <tableColumn id="2" xr3:uid="{2FD7451F-B63D-4E98-A795-D79A894B4E94}" name="Shift" dataDxfId="88" totalsRowDxfId="87"/>
+    <tableColumn id="3" xr3:uid="{A3D25D4C-366B-4D7B-84D3-B001BC845B0F}" name="Alt" dataDxfId="86" totalsRowDxfId="85"/>
+    <tableColumn id="4" xr3:uid="{71ED80D6-715B-4D58-BD43-ABA33B7EA76E}" name="Key" dataDxfId="84" totalsRowDxfId="83"/>
+    <tableColumn id="5" xr3:uid="{B8A9CB87-4538-4CB7-97B8-525338E383D6}" name="機能" dataDxfId="82" totalsRowDxfId="81"/>
+    <tableColumn id="7" xr3:uid="{06A85E02-878A-446D-B0C0-EDAC09D07E76}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="80" totalsRowDxfId="79" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル1713[[#This Row],[機能]]),"","|"&amp;テーブル1713[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル1713[[#This Row],[Shift]]&amp;"|"&amp;テーブル1713[[#This Row],[Alt]]&amp;"|"&amp;テーブル1713[[#This Row],[Key]]&amp;"|"&amp;テーブル1713[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14165,15 +14425,15 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{74162BA7-0E42-48B6-B99F-4D7F769D24F9}" name="テーブル1789" displayName="テーブル1789" ref="A1:F99" headerRowDxfId="65" dataDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{74162BA7-0E42-48B6-B99F-4D7F769D24F9}" name="テーブル1789" displayName="テーブル1789" ref="A1:F99" headerRowDxfId="78" dataDxfId="77">
   <autoFilter ref="A1:F99" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{62FA586D-EF03-4D43-A10E-78D2AF735C71}" name="Ctrl" totalsRowLabel="集計" dataDxfId="63" totalsRowDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{C5A7C3F6-4F42-4530-8FD3-1990CF3F9124}" name="Shift" dataDxfId="61" totalsRowDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{A05CE0D9-140D-45A0-888F-253BF948A770}" name="Alt" dataDxfId="59" totalsRowDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{7DA7D284-C06D-4102-9404-5695C13F122B}" name="Key" dataDxfId="57" totalsRowDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{3D010DA0-57B1-4C00-9C5F-DCCF15D9FD17}" name="機能" dataDxfId="55" totalsRowDxfId="54"/>
-    <tableColumn id="7" xr3:uid="{E74BE0E9-7F88-484C-9AEE-D35FA3AED34A}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="53" totalsRowDxfId="52" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{62FA586D-EF03-4D43-A10E-78D2AF735C71}" name="Ctrl" totalsRowLabel="集計" dataDxfId="76" totalsRowDxfId="75"/>
+    <tableColumn id="2" xr3:uid="{C5A7C3F6-4F42-4530-8FD3-1990CF3F9124}" name="Shift" dataDxfId="74" totalsRowDxfId="73"/>
+    <tableColumn id="3" xr3:uid="{A05CE0D9-140D-45A0-888F-253BF948A770}" name="Alt" dataDxfId="72" totalsRowDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{7DA7D284-C06D-4102-9404-5695C13F122B}" name="Key" dataDxfId="70" totalsRowDxfId="69"/>
+    <tableColumn id="5" xr3:uid="{3D010DA0-57B1-4C00-9C5F-DCCF15D9FD17}" name="機能" dataDxfId="68" totalsRowDxfId="67"/>
+    <tableColumn id="7" xr3:uid="{E74BE0E9-7F88-484C-9AEE-D35FA3AED34A}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="66" totalsRowDxfId="65" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル1789[[#This Row],[機能]]),"","|"&amp;テーブル1789[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル1789[[#This Row],[Shift]]&amp;"|"&amp;テーブル1789[[#This Row],[Alt]]&amp;"|"&amp;テーブル1789[[#This Row],[Key]]&amp;"|"&amp;テーブル1789[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14182,15 +14442,15 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E6EF7B9C-FAC1-42B1-BC95-AF668093141D}" name="テーブル1781011" displayName="テーブル1781011" ref="A1:F88" headerRowDxfId="51" dataDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E6EF7B9C-FAC1-42B1-BC95-AF668093141D}" name="テーブル1781011" displayName="テーブル1781011" ref="A1:F88" headerRowDxfId="64" dataDxfId="63">
   <autoFilter ref="A1:F88" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{10591B97-DA49-4E0D-BF23-0888174E098F}" name="Ctrl" totalsRowLabel="集計" dataDxfId="49" totalsRowDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{EDA168A4-45CB-47AC-9F73-DAC9B98B27C9}" name="Shift" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{3CB7FF1C-24DD-4B0B-8123-C85716EAD21F}" name="Alt" dataDxfId="46" totalsRowDxfId="45" dataCellStyle="標準 2"/>
-    <tableColumn id="4" xr3:uid="{8AEA5FCE-4FCC-42AA-A7BC-DD61C011D20F}" name="Key" dataDxfId="44" totalsRowDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{1A91CD22-6C43-43F8-AD49-13837BC29411}" name="機能" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{B88C40F9-0361-4D7D-B3EE-F9FB5D80EF07}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="40" totalsRowDxfId="39" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{10591B97-DA49-4E0D-BF23-0888174E098F}" name="Ctrl" totalsRowLabel="集計" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{EDA168A4-45CB-47AC-9F73-DAC9B98B27C9}" name="Shift" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{3CB7FF1C-24DD-4B0B-8123-C85716EAD21F}" name="Alt" dataDxfId="59" totalsRowDxfId="58" dataCellStyle="標準 2"/>
+    <tableColumn id="4" xr3:uid="{8AEA5FCE-4FCC-42AA-A7BC-DD61C011D20F}" name="Key" dataDxfId="57" totalsRowDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{1A91CD22-6C43-43F8-AD49-13837BC29411}" name="機能" dataDxfId="55" totalsRowDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{B88C40F9-0361-4D7D-B3EE-F9FB5D80EF07}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="53" totalsRowDxfId="52" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル1781011[[#This Row],[機能]]),"","|"&amp;テーブル1781011[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル1781011[[#This Row],[Shift]]&amp;"|"&amp;テーブル1781011[[#This Row],[Alt]]&amp;"|"&amp;テーブル1781011[[#This Row],[Key]]&amp;"|"&amp;テーブル1781011[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14199,15 +14459,15 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{B3B06C47-0783-4864-BFA7-B306B0811F6A}" name="テーブル178101117" displayName="テーブル178101117" ref="A1:F77" headerRowDxfId="38" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{B3B06C47-0783-4864-BFA7-B306B0811F6A}" name="テーブル178101117" displayName="テーブル178101117" ref="A1:F77" headerRowDxfId="51" dataDxfId="50">
   <autoFilter ref="A1:F77" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7074AF62-75A2-46EA-8E94-9E786E84646D}" name="Ctrl" totalsRowLabel="集計" dataDxfId="36" totalsRowDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{F02671C4-0209-4380-B7DA-CF9B477E89B2}" name="Shift" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{9B58AEF7-1D72-4FEE-A42F-93F443378C06}" name="Alt" dataDxfId="33" totalsRowDxfId="32" dataCellStyle="標準 2"/>
-    <tableColumn id="4" xr3:uid="{D6259F1A-DA1E-493E-8B9D-E5E7A7F4A237}" name="Key" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{845EF0DA-8876-435D-B447-45D9FDE96CB8}" name="機能" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{73F62DE7-8594-4C51-868E-0808EC9462FA}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="27" totalsRowDxfId="26" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{7074AF62-75A2-46EA-8E94-9E786E84646D}" name="Ctrl" totalsRowLabel="集計" dataDxfId="49" totalsRowDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{F02671C4-0209-4380-B7DA-CF9B477E89B2}" name="Shift" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{9B58AEF7-1D72-4FEE-A42F-93F443378C06}" name="Alt" dataDxfId="46" totalsRowDxfId="45" dataCellStyle="標準 2"/>
+    <tableColumn id="4" xr3:uid="{D6259F1A-DA1E-493E-8B9D-E5E7A7F4A237}" name="Key" dataDxfId="44" totalsRowDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{845EF0DA-8876-435D-B447-45D9FDE96CB8}" name="機能" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{73F62DE7-8594-4C51-868E-0808EC9462FA}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="40" totalsRowDxfId="39" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル178101117[[#This Row],[機能]]),"","|"&amp;テーブル178101117[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101117[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101117[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101117[[#This Row],[Key]]&amp;"|"&amp;テーブル178101117[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14216,15 +14476,15 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{3E4261FB-9C64-448C-9F25-19EE6AB0F0AD}" name="テーブル17810111718" displayName="テーブル17810111718" ref="A1:F87" headerRowDxfId="25" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{3E4261FB-9C64-448C-9F25-19EE6AB0F0AD}" name="テーブル17810111718" displayName="テーブル17810111718" ref="A1:F87" headerRowDxfId="38" dataDxfId="37">
   <autoFilter ref="A1:F87" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{162A6882-854C-4B36-BAC7-6242ED6FC9CA}" name="Ctrl" totalsRowLabel="集計" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{5A1827CA-FA25-42CF-8A80-A75C4BC329D4}" name="Shift" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{DE18CCD6-FA82-4E00-AAC1-C76845B9238E}" name="Alt" dataDxfId="20" totalsRowDxfId="19" dataCellStyle="標準 2"/>
-    <tableColumn id="4" xr3:uid="{0B51BB38-9C41-4F58-9BE6-6B40D4186466}" name="Key" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{25751899-D56F-4317-B3BB-BE7B6603B360}" name="機能" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{CC47A67F-93F0-47FE-ACDE-5B7D47EE09A3}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="14" totalsRowDxfId="13" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{162A6882-854C-4B36-BAC7-6242ED6FC9CA}" name="Ctrl" totalsRowLabel="集計" dataDxfId="36" totalsRowDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{5A1827CA-FA25-42CF-8A80-A75C4BC329D4}" name="Shift" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{DE18CCD6-FA82-4E00-AAC1-C76845B9238E}" name="Alt" dataDxfId="33" totalsRowDxfId="32" dataCellStyle="標準 2"/>
+    <tableColumn id="4" xr3:uid="{0B51BB38-9C41-4F58-9BE6-6B40D4186466}" name="Key" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{25751899-D56F-4317-B3BB-BE7B6603B360}" name="機能" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{CC47A67F-93F0-47FE-ACDE-5B7D47EE09A3}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="27" totalsRowDxfId="26" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル17810111718[[#This Row],[機能]]),"","|"&amp;テーブル17810111718[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル17810111718[[#This Row],[Shift]]&amp;"|"&amp;テーブル17810111718[[#This Row],[Alt]]&amp;"|"&amp;テーブル17810111718[[#This Row],[Key]]&amp;"|"&amp;テーブル17810111718[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14233,15 +14493,15 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{72618182-08FB-4942-8D51-0628E2D5519E}" name="テーブル1781011171819" displayName="テーブル1781011171819" ref="A1:F87" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{72618182-08FB-4942-8D51-0628E2D5519E}" name="テーブル1781011171819" displayName="テーブル1781011171819" ref="A1:F87" headerRowDxfId="25" dataDxfId="24">
   <autoFilter ref="A1:F87" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{1EC370EB-2CCF-471A-A9F1-8BFE3434C0C3}" name="Ctrl" totalsRowLabel="集計" dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{5C210C7B-C356-412C-AC20-253C981D7907}" name="Shift" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{F351B8B0-0AF7-4680-B5A4-8F602D63915D}" name="Alt" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="標準 2"/>
-    <tableColumn id="4" xr3:uid="{53558A0C-5166-4CAA-B9DD-A3B5CCA169BC}" name="Key" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{51E10D32-57E4-430D-8B5D-A54EA2FD9B5A}" name="機能" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{2753E847-69A8-4872-9DF2-860498E8FBE6}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="1" totalsRowDxfId="0" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{1EC370EB-2CCF-471A-A9F1-8BFE3434C0C3}" name="Ctrl" totalsRowLabel="集計" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{5C210C7B-C356-412C-AC20-253C981D7907}" name="Shift" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{F351B8B0-0AF7-4680-B5A4-8F602D63915D}" name="Alt" dataDxfId="20" totalsRowDxfId="19" dataCellStyle="標準 2"/>
+    <tableColumn id="4" xr3:uid="{53558A0C-5166-4CAA-B9DD-A3B5CCA169BC}" name="Key" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{51E10D32-57E4-430D-8B5D-A54EA2FD9B5A}" name="機能" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{2753E847-69A8-4872-9DF2-860498E8FBE6}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="14" totalsRowDxfId="13" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル1781011171819[[#This Row],[機能]]),"","|"&amp;テーブル1781011171819[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル1781011171819[[#This Row],[Shift]]&amp;"|"&amp;テーブル1781011171819[[#This Row],[Alt]]&amp;"|"&amp;テーブル1781011171819[[#This Row],[Key]]&amp;"|"&amp;テーブル1781011171819[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14249,23 +14509,40 @@
 </table>
 </file>
 
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{39A7D7A0-5CE2-4C8B-8A28-2BC6EC549635}" name="テーブル178101120" displayName="テーブル178101120" ref="A1:F55" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:F55" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{3830EEBC-154F-40A3-B087-489BFED09380}" name="Ctrl" totalsRowLabel="集計" dataDxfId="9" totalsRowDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{386AD76C-8DA4-43AD-9458-18CB394569D0}" name="Shift" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{B6E05D92-73F3-4E46-9C40-142C172FFE6F}" name="Alt" dataDxfId="6" totalsRowDxfId="7" dataCellStyle="標準 2"/>
+    <tableColumn id="4" xr3:uid="{001E3703-0DA4-4C1D-A14B-1A71D7D7575B}" name="Key" dataDxfId="4" totalsRowDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{799D3E19-1032-43A9-987E-28F24FD884E4}" name="機能" dataDxfId="2" totalsRowDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{55CDEF9E-B358-4E6D-8007-E8A0016CA0FA}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="0" totalsRowDxfId="1" dataCellStyle="標準 2">
+      <calculatedColumnFormula>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{2D9DF68C-926B-4ABF-87EC-2BE15B3EDBDB}" name="テーブル1716" displayName="テーブル1716" ref="A1:I93" headerRowDxfId="236" dataDxfId="235">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{2D9DF68C-926B-4ABF-87EC-2BE15B3EDBDB}" name="テーブル1716" displayName="テーブル1716" ref="A1:I93" headerRowDxfId="249" dataDxfId="248">
   <autoFilter ref="A1:I93" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{3E147AE7-D0C8-41DF-A4E2-0268C41F44F6}" name="Ctrl" totalsRowLabel="集計" dataDxfId="234" totalsRowDxfId="233"/>
-    <tableColumn id="2" xr3:uid="{4B9FC3C4-17EE-475E-9219-3391B5ABF30B}" name="Shift" dataDxfId="232" totalsRowDxfId="231"/>
-    <tableColumn id="3" xr3:uid="{46A18348-8F0B-4779-88BB-730AF7B856AC}" name="Alt" dataDxfId="230" totalsRowDxfId="229"/>
-    <tableColumn id="4" xr3:uid="{0F2B1969-7969-4132-96AD-0CA04323D1A0}" name="Key" dataDxfId="228" totalsRowDxfId="227"/>
-    <tableColumn id="5" xr3:uid="{0297C143-EEA0-428C-A549-6D4881A1076B}" name="機能" dataDxfId="226" totalsRowDxfId="225"/>
-    <tableColumn id="7" xr3:uid="{938135D4-7AE7-47A0-AD6A-EDEB24C14E63}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="224" totalsRowDxfId="223" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{3E147AE7-D0C8-41DF-A4E2-0268C41F44F6}" name="Ctrl" totalsRowLabel="集計" dataDxfId="247" totalsRowDxfId="246"/>
+    <tableColumn id="2" xr3:uid="{4B9FC3C4-17EE-475E-9219-3391B5ABF30B}" name="Shift" dataDxfId="245" totalsRowDxfId="244"/>
+    <tableColumn id="3" xr3:uid="{46A18348-8F0B-4779-88BB-730AF7B856AC}" name="Alt" dataDxfId="243" totalsRowDxfId="242"/>
+    <tableColumn id="4" xr3:uid="{0F2B1969-7969-4132-96AD-0CA04323D1A0}" name="Key" dataDxfId="241" totalsRowDxfId="240"/>
+    <tableColumn id="5" xr3:uid="{0297C143-EEA0-428C-A549-6D4881A1076B}" name="機能" dataDxfId="239" totalsRowDxfId="238"/>
+    <tableColumn id="7" xr3:uid="{938135D4-7AE7-47A0-AD6A-EDEB24C14E63}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="237" totalsRowDxfId="236" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル1716[[#This Row],[機能]]),"","|"&amp;テーブル1716[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル1716[[#This Row],[Shift]]&amp;"|"&amp;テーブル1716[[#This Row],[Alt]]&amp;"|"&amp;テーブル1716[[#This Row],[Key]]&amp;"|"&amp;テーブル1716[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{1E9D4DD2-9737-4143-957E-F319F30E0B34}" name="動作" dataDxfId="222" totalsRowDxfId="221" dataCellStyle="標準 2">
+    <tableColumn id="8" xr3:uid="{1E9D4DD2-9737-4143-957E-F319F30E0B34}" name="動作" dataDxfId="235" totalsRowDxfId="234" dataCellStyle="標準 2">
       <calculatedColumnFormula>テーブル1716[[#This Row],[機能]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{15AC32E6-0DDA-41BB-9F12-D1D0E6E9DB8B}" name="ソフト名" dataDxfId="220" totalsRowDxfId="219" dataCellStyle="標準 2"/>
-    <tableColumn id="6" xr3:uid="{F8D06D54-E796-4E6D-B14F-DAD3A48F2538}" name="ショートカットキー" dataDxfId="218" totalsRowDxfId="217">
+    <tableColumn id="9" xr3:uid="{15AC32E6-0DDA-41BB-9F12-D1D0E6E9DB8B}" name="ソフト名" dataDxfId="233" totalsRowDxfId="232" dataCellStyle="標準 2"/>
+    <tableColumn id="6" xr3:uid="{F8D06D54-E796-4E6D-B14F-DAD3A48F2538}" name="ショートカットキー" dataDxfId="231" totalsRowDxfId="230">
       <calculatedColumnFormula>IF(テーブル1716[[#This Row],[Ctrl]]="","",テーブル1716[[#This Row],[Ctrl]]&amp;"＋")&amp;
 IF(テーブル1716[[#This Row],[Shift]]="","",テーブル1716[[#This Row],[Shift]]&amp;"＋")&amp;
 IF(テーブル1716[[#This Row],[Alt]]="","",テーブル1716[[#This Row],[Alt]]&amp;"＋")&amp;テーブル1716[[#This Row],[Key]]</calculatedColumnFormula>
@@ -14276,15 +14553,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B5B3D110-E258-4597-BB86-3913C990E2CB}" name="テーブル17" displayName="テーブル17" ref="A1:F98" headerRowDxfId="216" dataDxfId="215">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B5B3D110-E258-4597-BB86-3913C990E2CB}" name="テーブル17" displayName="テーブル17" ref="A1:F98" headerRowDxfId="229" dataDxfId="228">
   <autoFilter ref="A1:F98" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{A339EFE5-6258-4149-86B3-E1CEAA4BEE00}" name="Ctrl" totalsRowLabel="集計" dataDxfId="214" totalsRowDxfId="213"/>
-    <tableColumn id="2" xr3:uid="{95FE279B-8D22-4BC8-8A2E-858DDB73272E}" name="Shift" dataDxfId="212" totalsRowDxfId="211"/>
-    <tableColumn id="3" xr3:uid="{38818F14-8583-4816-90BC-42EC8E0CEF9E}" name="Alt" dataDxfId="210" totalsRowDxfId="209"/>
-    <tableColumn id="4" xr3:uid="{59B72529-4238-4F15-B172-C15FB4893E65}" name="Key" dataDxfId="208" totalsRowDxfId="207"/>
-    <tableColumn id="5" xr3:uid="{1D07021F-1DC8-467F-922D-781773F86854}" name="機能" dataDxfId="206" totalsRowDxfId="205"/>
-    <tableColumn id="7" xr3:uid="{B99A910B-404C-4E9F-ABC8-6C1CF3E22617}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="204" totalsRowDxfId="203" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{A339EFE5-6258-4149-86B3-E1CEAA4BEE00}" name="Ctrl" totalsRowLabel="集計" dataDxfId="227" totalsRowDxfId="226"/>
+    <tableColumn id="2" xr3:uid="{95FE279B-8D22-4BC8-8A2E-858DDB73272E}" name="Shift" dataDxfId="225" totalsRowDxfId="224"/>
+    <tableColumn id="3" xr3:uid="{38818F14-8583-4816-90BC-42EC8E0CEF9E}" name="Alt" dataDxfId="223" totalsRowDxfId="222"/>
+    <tableColumn id="4" xr3:uid="{59B72529-4238-4F15-B172-C15FB4893E65}" name="Key" dataDxfId="221" totalsRowDxfId="220"/>
+    <tableColumn id="5" xr3:uid="{1D07021F-1DC8-467F-922D-781773F86854}" name="機能" dataDxfId="219" totalsRowDxfId="218"/>
+    <tableColumn id="7" xr3:uid="{B99A910B-404C-4E9F-ABC8-6C1CF3E22617}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="217" totalsRowDxfId="216" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル17[[#This Row],[機能]]),"","|"&amp;テーブル17[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル17[[#This Row],[Shift]]&amp;"|"&amp;テーブル17[[#This Row],[Alt]]&amp;"|"&amp;テーブル17[[#This Row],[Key]]&amp;"|"&amp;テーブル17[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14293,18 +14570,18 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3651D7F7-A056-4B9F-A254-BC10C8DFD165}" name="テーブル178" displayName="テーブル178" ref="A1:G105" headerRowDxfId="202" dataDxfId="201">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3651D7F7-A056-4B9F-A254-BC10C8DFD165}" name="テーブル178" displayName="テーブル178" ref="A1:G105" headerRowDxfId="215" dataDxfId="214">
   <autoFilter ref="A1:G105" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{68752F33-5B3F-4E9C-B091-B22CC2989F38}" name="Ctrl" totalsRowLabel="集計" dataDxfId="200" totalsRowDxfId="199"/>
-    <tableColumn id="2" xr3:uid="{5167CBDE-CFFA-48FA-949C-7754DEBB5471}" name="Shift" dataDxfId="198" totalsRowDxfId="197"/>
-    <tableColumn id="3" xr3:uid="{A2117648-5D51-418A-8399-3A653EB882CF}" name="Alt" dataDxfId="196" totalsRowDxfId="195"/>
-    <tableColumn id="4" xr3:uid="{2372578A-8AA5-480D-AA77-FC8F0A78D0EA}" name="Key" dataDxfId="194" totalsRowDxfId="193"/>
-    <tableColumn id="5" xr3:uid="{3BE13509-C9C9-46C8-8667-7EAECC678335}" name="機能" dataDxfId="192" totalsRowDxfId="191"/>
-    <tableColumn id="7" xr3:uid="{AE1A202E-0809-4E6C-9470-DFFA229D9669}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="190" totalsRowDxfId="189" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{68752F33-5B3F-4E9C-B091-B22CC2989F38}" name="Ctrl" totalsRowLabel="集計" dataDxfId="213" totalsRowDxfId="212"/>
+    <tableColumn id="2" xr3:uid="{5167CBDE-CFFA-48FA-949C-7754DEBB5471}" name="Shift" dataDxfId="211" totalsRowDxfId="210"/>
+    <tableColumn id="3" xr3:uid="{A2117648-5D51-418A-8399-3A653EB882CF}" name="Alt" dataDxfId="209" totalsRowDxfId="208"/>
+    <tableColumn id="4" xr3:uid="{2372578A-8AA5-480D-AA77-FC8F0A78D0EA}" name="Key" dataDxfId="207" totalsRowDxfId="206"/>
+    <tableColumn id="5" xr3:uid="{3BE13509-C9C9-46C8-8667-7EAECC678335}" name="機能" dataDxfId="205" totalsRowDxfId="204"/>
+    <tableColumn id="7" xr3:uid="{AE1A202E-0809-4E6C-9470-DFFA229D9669}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="203" totalsRowDxfId="202" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル178[[#This Row],[機能]]),"","|"&amp;テーブル178[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178[[#This Row],[Shift]]&amp;"|"&amp;テーブル178[[#This Row],[Alt]]&amp;"|"&amp;テーブル178[[#This Row],[Key]]&amp;"|"&amp;テーブル178[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4FE1A9C3-DE35-4CAE-87CE-F88C1F9C3BF9}" name="列1" dataDxfId="188" totalsRowDxfId="187">
+    <tableColumn id="6" xr3:uid="{4FE1A9C3-DE35-4CAE-87CE-F88C1F9C3BF9}" name="列1" dataDxfId="201" totalsRowDxfId="200">
       <calculatedColumnFormula>IF(テーブル178[[#This Row],[Ctrl]]="","",テーブル178[[#This Row],[Ctrl]]&amp;"＋")&amp;
 IF(テーブル178[[#This Row],[Shift]]="","",テーブル178[[#This Row],[Shift]]&amp;"＋")&amp;
 IF(テーブル178[[#This Row],[Alt]]="","",テーブル178[[#This Row],[Alt]]&amp;"＋")&amp;テーブル178[[#This Row],[Key]]</calculatedColumnFormula>
@@ -14315,12 +14592,12 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{20717FDD-4026-4F7F-936C-BEEC867C938B}" name="テーブル17814" displayName="テーブル17814" ref="A1:C92" headerRowDxfId="186" dataDxfId="185">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{20717FDD-4026-4F7F-936C-BEEC867C938B}" name="テーブル17814" displayName="テーブル17814" ref="A1:C92" headerRowDxfId="199" dataDxfId="198">
   <autoFilter ref="A1:C92" xr:uid="{4CB39E0E-759A-4F48-9321-000A7B6C0DCA}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{3AEEA09D-295D-4DA2-B1DC-7199FAFF0781}" name="Key" dataDxfId="184" totalsRowDxfId="183" dataCellStyle="標準 2"/>
-    <tableColumn id="5" xr3:uid="{A76CCD34-8166-44D0-8998-F212D2DFCFFB}" name="機能" dataDxfId="182" totalsRowDxfId="181" dataCellStyle="標準 2"/>
-    <tableColumn id="7" xr3:uid="{6F6BD55F-093D-4EEF-8239-C97ACF4A285C}" name="| Key | 機能 |" totalsRowFunction="count" dataDxfId="180" totalsRowDxfId="179" dataCellStyle="標準 2">
+    <tableColumn id="2" xr3:uid="{3AEEA09D-295D-4DA2-B1DC-7199FAFF0781}" name="Key" dataDxfId="197" totalsRowDxfId="196" dataCellStyle="標準 2"/>
+    <tableColumn id="5" xr3:uid="{A76CCD34-8166-44D0-8998-F212D2DFCFFB}" name="機能" dataDxfId="195" totalsRowDxfId="194" dataCellStyle="標準 2"/>
+    <tableColumn id="7" xr3:uid="{6F6BD55F-093D-4EEF-8239-C97ACF4A285C}" name="| Key | 機能 |" totalsRowFunction="count" dataDxfId="193" totalsRowDxfId="192" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル17814[[#This Row],[機能]]),"","|"&amp;テーブル17814[[#This Row],[Key]]&amp;"|"&amp;テーブル17814[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14329,15 +14606,15 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{CD3FDAAC-EA50-4891-82BC-D4E844A5127E}" name="テーブル17815" displayName="テーブル17815" ref="A1:F99" headerRowDxfId="178" dataDxfId="177">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{CD3FDAAC-EA50-4891-82BC-D4E844A5127E}" name="テーブル17815" displayName="テーブル17815" ref="A1:F99" headerRowDxfId="191" dataDxfId="190">
   <autoFilter ref="A1:F99" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{ABB88C56-03A7-4AE9-BC2E-9C94F6123CED}" name="Ctrl" totalsRowLabel="集計" dataDxfId="176" totalsRowDxfId="175"/>
-    <tableColumn id="2" xr3:uid="{54ED05C0-41E5-4D67-AC66-4C672B6FCEE0}" name="Shift" dataDxfId="174" totalsRowDxfId="173"/>
-    <tableColumn id="3" xr3:uid="{460AE638-8C55-41C3-AAF9-5CA7AE00D46C}" name="Alt" dataDxfId="172" totalsRowDxfId="171"/>
-    <tableColumn id="4" xr3:uid="{4A2D0730-8F61-4FC1-AD20-422CC8C8418A}" name="Key" dataDxfId="170" totalsRowDxfId="169"/>
-    <tableColumn id="5" xr3:uid="{52A22859-FCDA-42B4-A9B3-A252BE1722B5}" name="機能" dataDxfId="168" totalsRowDxfId="167"/>
-    <tableColumn id="7" xr3:uid="{FA9A7219-28FF-4D03-8D62-50F57A41243F}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="166" totalsRowDxfId="165" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{ABB88C56-03A7-4AE9-BC2E-9C94F6123CED}" name="Ctrl" totalsRowLabel="集計" dataDxfId="189" totalsRowDxfId="188"/>
+    <tableColumn id="2" xr3:uid="{54ED05C0-41E5-4D67-AC66-4C672B6FCEE0}" name="Shift" dataDxfId="187" totalsRowDxfId="186"/>
+    <tableColumn id="3" xr3:uid="{460AE638-8C55-41C3-AAF9-5CA7AE00D46C}" name="Alt" dataDxfId="185" totalsRowDxfId="184"/>
+    <tableColumn id="4" xr3:uid="{4A2D0730-8F61-4FC1-AD20-422CC8C8418A}" name="Key" dataDxfId="183" totalsRowDxfId="182"/>
+    <tableColumn id="5" xr3:uid="{52A22859-FCDA-42B4-A9B3-A252BE1722B5}" name="機能" dataDxfId="181" totalsRowDxfId="180"/>
+    <tableColumn id="7" xr3:uid="{FA9A7219-28FF-4D03-8D62-50F57A41243F}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="179" totalsRowDxfId="178" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル17815[[#This Row],[機能]]),"","|"&amp;テーブル17815[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル17815[[#This Row],[Shift]]&amp;"|"&amp;テーブル17815[[#This Row],[Alt]]&amp;"|"&amp;テーブル17815[[#This Row],[Key]]&amp;"|"&amp;テーブル17815[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14346,18 +14623,18 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{64C7855A-AE6E-4D1B-95FD-A0F7F70CC417}" name="テーブル1312" displayName="テーブル1312" ref="A1:G80" headerRowDxfId="164" dataDxfId="163">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{64C7855A-AE6E-4D1B-95FD-A0F7F70CC417}" name="テーブル1312" displayName="テーブル1312" ref="A1:G80" headerRowDxfId="177" dataDxfId="176">
   <autoFilter ref="A1:G80" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{3B675F56-1F29-4E78-BDB6-CA41FB9B1F5C}" name="Ctrl" totalsRowLabel="集計" dataDxfId="162" totalsRowDxfId="161"/>
-    <tableColumn id="2" xr3:uid="{B7008E7C-6419-42EC-940A-5B6A0748F5B1}" name="Shift" dataDxfId="160" totalsRowDxfId="159"/>
-    <tableColumn id="3" xr3:uid="{D10E9664-9EFA-48AC-A609-71DE9D6B26CA}" name="Alt" dataDxfId="158" totalsRowDxfId="157"/>
-    <tableColumn id="4" xr3:uid="{04E5B1BB-D2DF-4C83-97E5-127E5BD91A73}" name="Key" dataDxfId="156" totalsRowDxfId="155"/>
-    <tableColumn id="5" xr3:uid="{1EE32BB4-F6DB-4221-AFF6-F34183FE5769}" name="機能" dataDxfId="154" totalsRowDxfId="153"/>
-    <tableColumn id="7" xr3:uid="{3266105D-4A94-4CBB-8500-927634878533}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="152" totalsRowDxfId="151" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{3B675F56-1F29-4E78-BDB6-CA41FB9B1F5C}" name="Ctrl" totalsRowLabel="集計" dataDxfId="175" totalsRowDxfId="174"/>
+    <tableColumn id="2" xr3:uid="{B7008E7C-6419-42EC-940A-5B6A0748F5B1}" name="Shift" dataDxfId="173" totalsRowDxfId="172"/>
+    <tableColumn id="3" xr3:uid="{D10E9664-9EFA-48AC-A609-71DE9D6B26CA}" name="Alt" dataDxfId="171" totalsRowDxfId="170"/>
+    <tableColumn id="4" xr3:uid="{04E5B1BB-D2DF-4C83-97E5-127E5BD91A73}" name="Key" dataDxfId="169" totalsRowDxfId="168"/>
+    <tableColumn id="5" xr3:uid="{1EE32BB4-F6DB-4221-AFF6-F34183FE5769}" name="機能" dataDxfId="167" totalsRowDxfId="166"/>
+    <tableColumn id="7" xr3:uid="{3266105D-4A94-4CBB-8500-927634878533}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="165" totalsRowDxfId="164" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル1312[[#This Row],[機能]]),"","|"&amp;テーブル1312[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル1312[[#This Row],[Shift]]&amp;"|"&amp;テーブル1312[[#This Row],[Alt]]&amp;"|"&amp;テーブル1312[[#This Row],[Key]]&amp;"|"&amp;テーブル1312[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D6909347-BC13-4100-95FE-0E48520F1E01}" name="列1" dataDxfId="150" totalsRowDxfId="149">
+    <tableColumn id="6" xr3:uid="{D6909347-BC13-4100-95FE-0E48520F1E01}" name="列1" dataDxfId="163" totalsRowDxfId="162">
       <calculatedColumnFormula>IF(テーブル1312[[#This Row],[Ctrl]]="","",テーブル1312[[#This Row],[Ctrl]]&amp;"＋")&amp;
 IF(テーブル1312[[#This Row],[Shift]]="","",テーブル1312[[#This Row],[Shift]]&amp;"＋")&amp;
 IF(テーブル1312[[#This Row],[Alt]]="","",テーブル1312[[#This Row],[Alt]]&amp;"＋")&amp;テーブル1312[[#This Row],[Key]]</calculatedColumnFormula>
@@ -14368,15 +14645,15 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{0BE3AAD5-252A-42BC-B735-5702B821C9F5}" name="テーブル17810" displayName="テーブル17810" ref="A1:F40" headerRowDxfId="148" dataDxfId="147">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{0BE3AAD5-252A-42BC-B735-5702B821C9F5}" name="テーブル17810" displayName="テーブル17810" ref="A1:F40" headerRowDxfId="161" dataDxfId="160">
   <autoFilter ref="A1:F40" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{AC738BBB-3009-41EE-B57C-C49F293EF770}" name="Ctrl" totalsRowLabel="集計" dataDxfId="146" totalsRowDxfId="145"/>
-    <tableColumn id="2" xr3:uid="{0FA728AD-25AD-41FC-AC69-C8FD9D439BB0}" name="Shift" dataDxfId="144"/>
-    <tableColumn id="3" xr3:uid="{A5C1728F-F016-41C4-894F-916122C25955}" name="Alt" dataDxfId="143" totalsRowDxfId="142" dataCellStyle="標準 2"/>
-    <tableColumn id="4" xr3:uid="{7A760A73-B1FA-44DC-9BF4-F09C9E1325A2}" name="Key" dataDxfId="141" totalsRowDxfId="140"/>
-    <tableColumn id="5" xr3:uid="{99F9108C-C22A-4625-A879-60C0A5850F2D}" name="機能" dataDxfId="139" totalsRowDxfId="138"/>
-    <tableColumn id="7" xr3:uid="{0F2ABE32-0915-4657-86F2-4FEBDC3CD8A8}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="137" totalsRowDxfId="136" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{AC738BBB-3009-41EE-B57C-C49F293EF770}" name="Ctrl" totalsRowLabel="集計" dataDxfId="159" totalsRowDxfId="158"/>
+    <tableColumn id="2" xr3:uid="{0FA728AD-25AD-41FC-AC69-C8FD9D439BB0}" name="Shift" dataDxfId="157"/>
+    <tableColumn id="3" xr3:uid="{A5C1728F-F016-41C4-894F-916122C25955}" name="Alt" dataDxfId="156" totalsRowDxfId="155" dataCellStyle="標準 2"/>
+    <tableColumn id="4" xr3:uid="{7A760A73-B1FA-44DC-9BF4-F09C9E1325A2}" name="Key" dataDxfId="154" totalsRowDxfId="153"/>
+    <tableColumn id="5" xr3:uid="{99F9108C-C22A-4625-A879-60C0A5850F2D}" name="機能" dataDxfId="152" totalsRowDxfId="151"/>
+    <tableColumn id="7" xr3:uid="{0F2ABE32-0915-4657-86F2-4FEBDC3CD8A8}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="150" totalsRowDxfId="149" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル17810[[#This Row],[機能]]),"","|"&amp;テーブル17810[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル17810[[#This Row],[Shift]]&amp;"|"&amp;テーブル17810[[#This Row],[Alt]]&amp;"|"&amp;テーブル17810[[#This Row],[Key]]&amp;"|"&amp;テーブル17810[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14385,15 +14662,15 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="テーブル134" displayName="テーブル134" ref="A1:F91" headerRowDxfId="135" dataDxfId="134">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="テーブル134" displayName="テーブル134" ref="A1:F91" headerRowDxfId="148" dataDxfId="147">
   <autoFilter ref="A1:F91" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Ctrl" totalsRowLabel="集計" dataDxfId="133" totalsRowDxfId="132"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Shift" dataDxfId="131" totalsRowDxfId="130"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Alt" dataDxfId="129" totalsRowDxfId="128"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Key" dataDxfId="127" totalsRowDxfId="126"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="機能" dataDxfId="125" totalsRowDxfId="124"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="123" totalsRowDxfId="122" dataCellStyle="標準 2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Ctrl" totalsRowLabel="集計" dataDxfId="146" totalsRowDxfId="145"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Shift" dataDxfId="144" totalsRowDxfId="143"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Alt" dataDxfId="142" totalsRowDxfId="141"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Key" dataDxfId="140" totalsRowDxfId="139"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="機能" dataDxfId="138" totalsRowDxfId="137"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="|Ctrl|Shift|Alt|Key|機能|" totalsRowFunction="count" dataDxfId="136" totalsRowDxfId="135" dataCellStyle="標準 2">
       <calculatedColumnFormula>IF(ISBLANK(テーブル134[[#This Row],[機能]]),"","|"&amp;テーブル134[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル134[[#This Row],[Shift]]&amp;"|"&amp;テーブル134[[#This Row],[Alt]]&amp;"|"&amp;テーブル134[[#This Row],[Key]]&amp;"|"&amp;テーブル134[[#This Row],[機能]]&amp;"|")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -30537,7 +30814,7 @@
       <c r="F57" s="12" t="s">
         <v>902</v>
       </c>
-      <c r="G57" s="64" t="s">
+      <c r="G57" s="12" t="s">
         <v>1815</v>
       </c>
       <c r="H57" s="12" t="s">
@@ -30972,10 +31249,10 @@
       <c r="F72" s="12" t="s">
         <v>1811</v>
       </c>
-      <c r="G72" s="64" t="s">
+      <c r="G72" s="12" t="s">
         <v>1812</v>
       </c>
-      <c r="H72" s="63" t="s">
+      <c r="H72" s="12" t="s">
         <v>1813</v>
       </c>
       <c r="I72" s="27" t="s">
@@ -57540,6 +57817,416 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65EB5390-8DA6-47CD-A71D-4560BC1C6FA5}">
+  <sheetPr>
+    <tabColor theme="8" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:F55"/>
+  <sheetFormatPr defaultColWidth="2" defaultRowHeight="11.25" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="6.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="42.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="50.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="2" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="11.25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="1.9" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v>|:---|:---|:---|:---|:---|</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="11.25" customHeight="1">
+      <c r="D3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v>||||Tab|オブジェクトモード/編集モード切替|</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="11.25" customHeight="1">
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="F4" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v>||Shift||Space|オブジェクトのモード(例: 移動/回転)切替え|</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="11.25" customHeight="1">
+      <c r="F5" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="11.25" customHeight="1">
+      <c r="F6" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="11.25" customHeight="1">
+      <c r="F7" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="11.25" customHeight="1">
+      <c r="F8" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="11.25" customHeight="1">
+      <c r="F9" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="11.25" customHeight="1">
+      <c r="F10" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="11.25" customHeight="1">
+      <c r="F11" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="11.25" customHeight="1">
+      <c r="F12" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="11.25" customHeight="1">
+      <c r="F13" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="11.25" customHeight="1">
+      <c r="F14" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="11.25" customHeight="1">
+      <c r="F15" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="11.25" customHeight="1">
+      <c r="F16" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F17" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F18" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F19" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F20" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F21" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F22" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F23" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F24" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F25" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F26" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F27" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F28" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F29" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F30" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F31" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F32" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F33" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F34" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F35" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F36" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F37" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F38" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F39" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F40" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F41" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F42" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F43" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F44" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F45" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F46" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F47" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F48" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F49" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F50" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F51" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F52" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F53" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F54" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="6:6" ht="11.25" customHeight="1">
+      <c r="F55" s="3" t="str">
+        <f>IF(ISBLANK(テーブル178101120[[#This Row],[機能]]),"","|"&amp;テーブル178101120[[#This Row],[Ctrl]]&amp;"|"&amp;テーブル178101120[[#This Row],[Shift]]&amp;"|"&amp;テーブル178101120[[#This Row],[Alt]]&amp;"|"&amp;テーブル178101120[[#This Row],[Key]]&amp;"|"&amp;テーブル178101120[[#This Row],[機能]]&amp;"|")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A54" xr:uid="{2C5FAE5B-AA20-47EA-BBE9-C95054B7167F}">
+      <formula1>"Ctrl"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B54" xr:uid="{0238CCEF-0082-4F3E-90DA-CC9C8D68A2B1}">
+      <formula1>"Shift"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C54" xr:uid="{1B336403-E36A-4B26-A2E0-065840BDD751}">
+      <formula1>"Alt"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
